--- a/data/availability/projects/la-vista-developments/el-patio-sola.xlsx
+++ b/data/availability/projects/la-vista-developments/el-patio-sola.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
